--- a/Configs/GameConfig/Datas/实体.xlsx
+++ b/Configs/GameConfig/Datas/实体.xlsx
@@ -1111,7 +1111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="9.225" customWidth="1" style="13" min="1" max="1"/>
@@ -1341,6 +1341,29 @@
         <v>0</v>
       </c>
     </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DemonMonkey</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>res://TheGame/Entitys/DemonMonkeyEntity.tscn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Actor</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="M1:N1"/>

--- a/Configs/GameConfig/Datas/实体.xlsx
+++ b/Configs/GameConfig/Datas/实体.xlsx
@@ -1111,7 +1111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="9.225" customWidth="1" style="13" min="1" max="1"/>
@@ -1364,6 +1364,29 @@
         <v>0</v>
       </c>
     </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Gorilla</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>res://TheGame/Entitys/GorillaEntity.tscn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Actor</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="M1:N1"/>
